--- a/database_penyimpanan_aman/database_timesheet_history.xlsx
+++ b/database_penyimpanan_aman/database_timesheet_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU2"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -652,11 +652,31 @@
           <t>Day_31</t>
         </is>
       </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>Nomor PO</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>Skema Sewa</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>Volume_Quantity</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>Satuan</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-18 13:48:38</t>
+          <t>2026-08-20 10:02:03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -686,23 +706,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Juli 2026</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>01 s/d 31 Juli 2026</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -729,12 +745,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>O</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>O</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -754,17 +770,17 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>S</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>S</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>S</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -779,12 +795,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>S</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>S</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -799,7 +815,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>S</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -809,17 +825,17 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>S</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>S</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>S</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -829,42 +845,42 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>S</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>S</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>S</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>S</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>S</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>S</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>S</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>S</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
@@ -875,6 +891,24 @@
       <c r="AU2" t="inlineStr">
         <is>
           <t>O</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>4500011424</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>31</v>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Hari</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_timesheet_history.xlsx
+++ b/database_penyimpanan_aman/database_timesheet_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -676,18 +676,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-20 10:02:03</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>042/BSS-JOB/AB/VII/2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>7207250142</t>
-        </is>
+          <t>2026-08-20 11:13:23</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>7207250142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -893,10 +887,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>4500011424</t>
-        </is>
+      <c r="AV2" t="n">
+        <v>4500011424</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
@@ -907,6 +899,245 @@
         <v>31</v>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Hari</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-20 11:21:13</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Man Lift Capacity 227 Kg</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>01 s/d 31 Juli 2026</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>16</v>
+      </c>
+      <c r="K3" t="n">
+        <v>15</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Elvira Sutrisno</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Ireine Langi</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>4500011425</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="AX3" t="n">
+        <v>31</v>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Hari</t>
         </is>

--- a/database_penyimpanan_aman/database_timesheet_history.xlsx
+++ b/database_penyimpanan_aman/database_timesheet_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -676,7 +676,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-20 11:13:23</t>
+          <t>2026-08-20 11:21:13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -695,7 +695,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Backhoe Loader</t>
+          <t>Man Lift Capacity 227 Kg</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -706,10 +706,10 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -739,12 +739,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>S</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>S</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>S</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>S</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -789,12 +789,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>O</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>O</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>O</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>O</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>O</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -854,17 +854,17 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>O</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>O</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>O</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>S</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="AV2" t="n">
-        <v>4500011424</v>
+        <v>4500011425</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
@@ -907,14 +907,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-20 11:21:13</t>
+          <t>2026-08-20 13:41:20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>7207250142</t>
-        </is>
+      <c r="C3" t="n">
+        <v>7207250142</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -928,7 +926,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Man Lift Capacity 227 Kg</t>
+          <t>Backhoe Loader</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -937,16 +935,12 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -976,12 +970,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>O</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>O</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -991,7 +985,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>O</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -1016,7 +1010,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>O</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1026,12 +1020,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>S</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>S</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1046,7 +1040,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>S</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1056,7 +1050,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>S</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1066,7 +1060,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>S</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1091,17 +1085,17 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>S</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>S</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>S</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1116,7 +1110,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>O</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1124,10 +1118,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>4500011425</t>
-        </is>
+      <c r="AV3" t="n">
+        <v>4500011424</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
@@ -1138,6 +1130,472 @@
         <v>31</v>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Hari</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:49:02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>7207250142</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vacuum Truck 10.000 L</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>01 s/d 31 Juli 2026</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L4" t="n">
+        <v>17</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Elvira Sutrisno</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Ireine Langi</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AV4" t="n">
+        <v>4500011426</v>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="AX4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Hari</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:05:10</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Truck Mounted Crane (TMC) Capacity 8 T</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>01 s/d 31 Juli 2026</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>13</v>
+      </c>
+      <c r="K5" t="n">
+        <v>18</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Elvira Sutrisno</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Ireine Langi</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>4500011424</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="AX5" t="n">
+        <v>31</v>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Hari</t>
         </is>

--- a/database_penyimpanan_aman/database_timesheet_history.xlsx
+++ b/database_penyimpanan_aman/database_timesheet_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1373,10 +1373,8 @@
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>7207250142</t>
-        </is>
+      <c r="C5" t="n">
+        <v>7207250142</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1582,10 +1580,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>4500011424</t>
-        </is>
+      <c r="AV5" t="n">
+        <v>4500011424</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
@@ -1598,6 +1594,480 @@
       <c r="AY5" t="inlineStr">
         <is>
           <t>Hari</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-22 16:03:27</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>7203250036</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Forklift Caterpiler Kap 5 Ton No FK.05</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>01 s/d 31 Juli 2026</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sewa Alat Forklift Kapasitas 5 ton untuk JOB Tomori </t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>18</v>
+      </c>
+      <c r="K6" t="n">
+        <v>12</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Elvira Sutrisno</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Ireine Langi</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="AV6" t="n">
+        <v>4500010848</v>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-22 16:06:22</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>7203250036</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Forklift Caterpiler Kap 5 Ton No FK.04</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>01 s/d 31 Juli 2026</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sewa Alat Forklift Kapasitas 5 ton untuk JOB Tomori </t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>18</v>
+      </c>
+      <c r="K7" t="n">
+        <v>12</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Elvira Sutrisno</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Ireine Langi</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>4500010848</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Unit</t>
         </is>
       </c>
     </row>
